--- a/Cosmetici/Fiscal/2026-09/Relacao_Saidas_Cosmetici_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Relacao_Saidas_Cosmetici_09-2026.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saídas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Saídas'!$A$4:$AA$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Saídas'!$A$4:$AC$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA109"/>
+  <dimension ref="A1:AC109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,9 @@
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="30" customWidth="1" min="26" max="26"/>
-    <col width="46" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
+    <col width="60" customWidth="1" min="28" max="28"/>
+    <col width="46" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,6 +668,16 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Conferência XML x Faturamento x Registro (ERP)</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>Análise (informativa - segue o XML)</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>Chave de acesso</t>
         </is>
@@ -722,6 +734,12 @@
       </c>
       <c r="AA5" s="5" t="inlineStr">
         <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AB5" s="5" t="inlineStr"/>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
           <t>Protocolo 141260351772358</t>
         </is>
       </c>
@@ -825,6 +843,16 @@
       </c>
       <c r="AA6" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB6" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] Industrialização sem insumo: CFOP 5124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês - informativo (escriturado conforme o XML, CFOP 5124) | [MÉDIA] Diferimento 5124: 5124 para PR com CST 00 (ICMS R$ 108.44) enquanto 35 itens 5124 do mês saíram com diferimento (CST 51). Conferir se o diferimento se aplica a este cliente | [BAIXA] Grupo IPI: 2 it</t>
+        </is>
+      </c>
+      <c r="AC6" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089391000116135</t>
         </is>
       </c>
@@ -928,6 +956,12 @@
       </c>
       <c r="AA7" s="5" t="inlineStr">
         <is>
+          <t>cancelada - fora dos dois relatórios (filtro "Situação A")</t>
+        </is>
+      </c>
+      <c r="AB7" s="5" t="inlineStr"/>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089401000115920</t>
         </is>
       </c>
@@ -1031,6 +1065,12 @@
       </c>
       <c r="AA8" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB8" s="5" t="inlineStr"/>
+      <c r="AC8" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089411000115935</t>
         </is>
       </c>
@@ -1134,6 +1174,12 @@
       </c>
       <c r="AA9" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB9" s="5" t="inlineStr"/>
+      <c r="AC9" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089421000115940</t>
         </is>
       </c>
@@ -1237,6 +1283,12 @@
       </c>
       <c r="AA10" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB10" s="5" t="inlineStr"/>
+      <c r="AC10" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089431000115891</t>
         </is>
       </c>
@@ -1340,6 +1392,12 @@
       </c>
       <c r="AA11" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB11" s="5" t="inlineStr"/>
+      <c r="AC11" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089441000115902</t>
         </is>
       </c>
@@ -1443,6 +1501,12 @@
       </c>
       <c r="AA12" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB12" s="5" t="inlineStr"/>
+      <c r="AC12" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089451000115918</t>
         </is>
       </c>
@@ -1546,6 +1610,12 @@
       </c>
       <c r="AA13" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB13" s="5" t="inlineStr"/>
+      <c r="AC13" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089461000196494</t>
         </is>
       </c>
@@ -1648,6 +1718,12 @@
         </is>
       </c>
       <c r="AA14" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB14" s="5" t="inlineStr"/>
+      <c r="AC14" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089471000196505</t>
         </is>
@@ -1704,6 +1780,12 @@
       </c>
       <c r="AA15" s="5" t="inlineStr">
         <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AB15" s="5" t="inlineStr"/>
+      <c r="AC15" s="5" t="inlineStr">
+        <is>
           <t>Protocolo 141260353599070</t>
         </is>
       </c>
@@ -1807,6 +1889,12 @@
       </c>
       <c r="AA16" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB16" s="5" t="inlineStr"/>
+      <c r="AC16" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089491000204197</t>
         </is>
       </c>
@@ -1909,6 +1997,12 @@
         </is>
       </c>
       <c r="AA17" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB17" s="5" t="inlineStr"/>
+      <c r="AC17" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089501000204201</t>
         </is>
@@ -1965,6 +2059,12 @@
       </c>
       <c r="AA18" s="5" t="inlineStr">
         <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AB18" s="5" t="inlineStr"/>
+      <c r="AC18" s="5" t="inlineStr">
+        <is>
           <t>Protocolo 141260353639120</t>
         </is>
       </c>
@@ -2068,6 +2168,12 @@
       </c>
       <c r="AA19" s="5" t="inlineStr">
         <is>
+          <t>cancelada - fora dos dois relatórios (filtro "Situação A")</t>
+        </is>
+      </c>
+      <c r="AB19" s="5" t="inlineStr"/>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089521000162996</t>
         </is>
       </c>
@@ -2171,6 +2277,12 @@
       </c>
       <c r="AA20" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB20" s="5" t="inlineStr"/>
+      <c r="AC20" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089531000163000</t>
         </is>
       </c>
@@ -2274,6 +2386,12 @@
       </c>
       <c r="AA21" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB21" s="5" t="inlineStr"/>
+      <c r="AC21" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089541000163016</t>
         </is>
       </c>
@@ -2376,6 +2494,12 @@
         </is>
       </c>
       <c r="AA22" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB22" s="5" t="inlineStr"/>
+      <c r="AC22" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089551000161819</t>
         </is>
@@ -2432,6 +2556,12 @@
       </c>
       <c r="AA23" s="5" t="inlineStr">
         <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AB23" s="5" t="inlineStr"/>
+      <c r="AC23" s="5" t="inlineStr">
+        <is>
           <t>Protocolo 141260355633030</t>
         </is>
       </c>
@@ -2535,6 +2665,12 @@
       </c>
       <c r="AA24" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB24" s="5" t="inlineStr"/>
+      <c r="AC24" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089571000162992</t>
         </is>
       </c>
@@ -2638,6 +2774,12 @@
       </c>
       <c r="AA25" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB25" s="5" t="inlineStr"/>
+      <c r="AC25" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089581000163007</t>
         </is>
       </c>
@@ -2741,6 +2883,12 @@
       </c>
       <c r="AA26" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB26" s="5" t="inlineStr"/>
+      <c r="AC26" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089591000156962</t>
         </is>
       </c>
@@ -2844,6 +2992,12 @@
       </c>
       <c r="AA27" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB27" s="5" t="inlineStr"/>
+      <c r="AC27" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089601000156971</t>
         </is>
       </c>
@@ -2947,6 +3101,12 @@
       </c>
       <c r="AA28" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB28" s="5" t="inlineStr"/>
+      <c r="AC28" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089611000197772</t>
         </is>
       </c>
@@ -3050,6 +3210,12 @@
       </c>
       <c r="AA29" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB29" s="5" t="inlineStr"/>
+      <c r="AC29" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089621000197788</t>
         </is>
       </c>
@@ -3153,6 +3319,12 @@
       </c>
       <c r="AA30" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB30" s="5" t="inlineStr"/>
+      <c r="AC30" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089631000118800</t>
         </is>
       </c>
@@ -3255,6 +3427,12 @@
         </is>
       </c>
       <c r="AA31" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB31" s="5" t="inlineStr"/>
+      <c r="AC31" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089641000118815</t>
         </is>
@@ -3311,6 +3489,12 @@
       </c>
       <c r="AA32" s="5" t="inlineStr">
         <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AB32" s="5" t="inlineStr"/>
+      <c r="AC32" s="5" t="inlineStr">
+        <is>
           <t>Protocolo 141260363749669</t>
         </is>
       </c>
@@ -3414,6 +3598,12 @@
       </c>
       <c r="AA33" s="5" t="inlineStr">
         <is>
+          <t>Registro: UF PR x XML SP</t>
+        </is>
+      </c>
+      <c r="AB33" s="5" t="inlineStr"/>
+      <c r="AC33" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089661000161928</t>
         </is>
       </c>
@@ -3517,6 +3707,16 @@
       </c>
       <c r="AA34" s="5" t="inlineStr">
         <is>
+          <t>Registro: UF PR x XML SP</t>
+        </is>
+      </c>
+      <c r="AB34" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 6102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC34" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089671000161933</t>
         </is>
       </c>
@@ -3620,6 +3820,12 @@
       </c>
       <c r="AA35" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB35" s="5" t="inlineStr"/>
+      <c r="AC35" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089681000161949</t>
         </is>
       </c>
@@ -3723,6 +3929,16 @@
       </c>
       <c r="AA36" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB36" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC36" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089691000161954</t>
         </is>
       </c>
@@ -3826,6 +4042,12 @@
       </c>
       <c r="AA37" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB37" s="5" t="inlineStr"/>
+      <c r="AC37" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089701000116445</t>
         </is>
       </c>
@@ -3929,6 +4151,12 @@
       </c>
       <c r="AA38" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB38" s="5" t="inlineStr"/>
+      <c r="AC38" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089711000207812</t>
         </is>
       </c>
@@ -4032,6 +4260,16 @@
       </c>
       <c r="AA39" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB39" s="5" t="inlineStr">
+        <is>
+          <t>[BAIXA] Grupo IPI: 2 item(ns) de produto (CFOP 6124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+        </is>
+      </c>
+      <c r="AC39" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089731000116625</t>
         </is>
       </c>
@@ -4135,6 +4373,12 @@
       </c>
       <c r="AA40" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB40" s="5" t="inlineStr"/>
+      <c r="AC40" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089741000116630</t>
         </is>
       </c>
@@ -4238,6 +4482,12 @@
       </c>
       <c r="AA41" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB41" s="5" t="inlineStr"/>
+      <c r="AC41" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089751000191575</t>
         </is>
       </c>
@@ -4341,6 +4591,12 @@
       </c>
       <c r="AA42" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB42" s="5" t="inlineStr"/>
+      <c r="AC42" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089761000191580</t>
         </is>
       </c>
@@ -4444,6 +4700,12 @@
       </c>
       <c r="AA43" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB43" s="5" t="inlineStr"/>
+      <c r="AC43" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089771000191596</t>
         </is>
       </c>
@@ -4546,6 +4808,16 @@
         </is>
       </c>
       <c r="AA44" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB44" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 9 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC44" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089781000162046</t>
         </is>
@@ -4602,6 +4874,12 @@
       </c>
       <c r="AA45" s="5" t="inlineStr">
         <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AB45" s="5" t="inlineStr"/>
+      <c r="AC45" s="5" t="inlineStr">
+        <is>
           <t>Protocolo 141260375536433</t>
         </is>
       </c>
@@ -4705,6 +4983,16 @@
       </c>
       <c r="AA46" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB46" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] Industrialização sem insumo: CFOP 6124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês - informativo (escriturado conforme o XML, CFOP 6124)</t>
+        </is>
+      </c>
+      <c r="AC46" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089791000217000</t>
         </is>
       </c>
@@ -4808,6 +5096,16 @@
       </c>
       <c r="AA47" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB47" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 19 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS" | [BAIXA] Grupo IPI: 3 item(ns) de produto (CFOP 5102) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+        </is>
+      </c>
+      <c r="AC47" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089801000162060</t>
         </is>
       </c>
@@ -4911,6 +5209,16 @@
       </c>
       <c r="AA48" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB48" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC48" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089811000162076</t>
         </is>
       </c>
@@ -5014,6 +5322,16 @@
       </c>
       <c r="AA49" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB49" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC49" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089821000162081</t>
         </is>
       </c>
@@ -5117,6 +5435,12 @@
       </c>
       <c r="AA50" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB50" s="5" t="inlineStr"/>
+      <c r="AC50" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089831000120041</t>
         </is>
       </c>
@@ -5220,6 +5544,12 @@
       </c>
       <c r="AA51" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB51" s="5" t="inlineStr"/>
+      <c r="AC51" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089841000120057</t>
         </is>
       </c>
@@ -5323,6 +5653,12 @@
       </c>
       <c r="AA52" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB52" s="5" t="inlineStr"/>
+      <c r="AC52" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089851000116375</t>
         </is>
       </c>
@@ -5426,6 +5762,12 @@
       </c>
       <c r="AA53" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB53" s="5" t="inlineStr"/>
+      <c r="AC53" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089861000116380</t>
         </is>
       </c>
@@ -5529,6 +5871,12 @@
       </c>
       <c r="AA54" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB54" s="5" t="inlineStr"/>
+      <c r="AC54" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089871000126294</t>
         </is>
       </c>
@@ -5632,6 +5980,12 @@
       </c>
       <c r="AA55" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB55" s="5" t="inlineStr"/>
+      <c r="AC55" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089881000126305</t>
         </is>
       </c>
@@ -5735,6 +6089,16 @@
       </c>
       <c r="AA56" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB56" s="5" t="inlineStr">
+        <is>
+          <t>[ALTA] Industrialização x retorno: Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 8993 (5902). Retorno de insumo é 5902/6902; como está, R$ 600.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
+        </is>
+      </c>
+      <c r="AC56" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089891000116358</t>
         </is>
       </c>
@@ -5838,6 +6202,12 @@
       </c>
       <c r="AA57" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB57" s="5" t="inlineStr"/>
+      <c r="AC57" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089901000207184</t>
         </is>
       </c>
@@ -5941,6 +6311,12 @@
       </c>
       <c r="AA58" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB58" s="5" t="inlineStr"/>
+      <c r="AC58" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089911000207190</t>
         </is>
       </c>
@@ -6044,6 +6420,12 @@
       </c>
       <c r="AA59" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB59" s="5" t="inlineStr"/>
+      <c r="AC59" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089921000116388</t>
         </is>
       </c>
@@ -6147,6 +6529,12 @@
       </c>
       <c r="AA60" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB60" s="5" t="inlineStr"/>
+      <c r="AC60" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089931000116393</t>
         </is>
       </c>
@@ -6250,6 +6638,12 @@
       </c>
       <c r="AA61" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB61" s="5" t="inlineStr"/>
+      <c r="AC61" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089941000166452</t>
         </is>
       </c>
@@ -6353,6 +6747,12 @@
       </c>
       <c r="AA62" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB62" s="5" t="inlineStr"/>
+      <c r="AC62" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089951000166468</t>
         </is>
       </c>
@@ -6456,6 +6856,12 @@
       </c>
       <c r="AA63" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB63" s="5" t="inlineStr"/>
+      <c r="AC63" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089961000197247</t>
         </is>
       </c>
@@ -6559,6 +6965,12 @@
       </c>
       <c r="AA64" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB64" s="5" t="inlineStr"/>
+      <c r="AC64" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089971000197252</t>
         </is>
       </c>
@@ -6662,6 +7074,12 @@
       </c>
       <c r="AA65" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB65" s="5" t="inlineStr"/>
+      <c r="AC65" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089981000186398</t>
         </is>
       </c>
@@ -6765,6 +7183,16 @@
       </c>
       <c r="AA66" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB66" s="5" t="inlineStr">
+        <is>
+          <t>[ALTA] Industrialização x retorno: Item 1 (FRASCO IMPRESSO OX 20V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 6124 de industrialização - o mesmo item foi devolvido também na NF 9005 (6902). Retorno de insumo é 5902/6902; como está, R$ 948.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
+        </is>
+      </c>
+      <c r="AC66" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000089991000116443</t>
         </is>
       </c>
@@ -6868,6 +7296,16 @@
       </c>
       <c r="AA67" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB67" s="5" t="inlineStr">
+        <is>
+          <t>[ALTA] Industrialização x retorno: Item 1 (FRASCO IMPRESSO OX 20V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 9002 (5902). Retorno de insumo é 5902/6902; como está, R$ 556.50 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
+        </is>
+      </c>
+      <c r="AC67" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090001000116462</t>
         </is>
       </c>
@@ -6971,6 +7409,12 @@
       </c>
       <c r="AA68" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB68" s="5" t="inlineStr"/>
+      <c r="AC68" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090011000116478</t>
         </is>
       </c>
@@ -7074,6 +7518,12 @@
       </c>
       <c r="AA69" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB69" s="5" t="inlineStr"/>
+      <c r="AC69" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090021000116483</t>
         </is>
       </c>
@@ -7177,6 +7627,16 @@
       </c>
       <c r="AA70" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB70" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 4 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC70" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090031000162296</t>
         </is>
       </c>
@@ -7280,6 +7740,12 @@
       </c>
       <c r="AA71" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB71" s="5" t="inlineStr"/>
+      <c r="AC71" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090041000116496</t>
         </is>
       </c>
@@ -7383,6 +7849,12 @@
       </c>
       <c r="AA72" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB72" s="5" t="inlineStr"/>
+      <c r="AC72" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090051000116507</t>
         </is>
       </c>
@@ -7486,6 +7958,16 @@
       </c>
       <c r="AA73" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB73" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC73" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090061000162328</t>
         </is>
       </c>
@@ -7589,6 +8071,12 @@
       </c>
       <c r="AA74" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB74" s="5" t="inlineStr"/>
+      <c r="AC74" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090071000170263</t>
         </is>
       </c>
@@ -7692,6 +8180,12 @@
       </c>
       <c r="AA75" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB75" s="5" t="inlineStr"/>
+      <c r="AC75" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090081000170279</t>
         </is>
       </c>
@@ -7795,6 +8289,16 @@
       </c>
       <c r="AA76" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB76" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 5 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC76" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090091000162354</t>
         </is>
       </c>
@@ -7898,6 +8402,12 @@
       </c>
       <c r="AA77" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB77" s="5" t="inlineStr"/>
+      <c r="AC77" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090101000217818</t>
         </is>
       </c>
@@ -8001,6 +8511,12 @@
       </c>
       <c r="AA78" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB78" s="5" t="inlineStr"/>
+      <c r="AC78" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090111000162379</t>
         </is>
       </c>
@@ -8104,6 +8620,12 @@
       </c>
       <c r="AA79" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB79" s="5" t="inlineStr"/>
+      <c r="AC79" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090121000217839</t>
         </is>
       </c>
@@ -8207,6 +8729,16 @@
       </c>
       <c r="AA80" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB80" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC80" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090131000162390</t>
         </is>
       </c>
@@ -8310,6 +8842,16 @@
       </c>
       <c r="AA81" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB81" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC81" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090141000162400</t>
         </is>
       </c>
@@ -8413,6 +8955,12 @@
       </c>
       <c r="AA82" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB82" s="5" t="inlineStr"/>
+      <c r="AC82" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090151000189365</t>
         </is>
       </c>
@@ -8516,6 +9064,12 @@
       </c>
       <c r="AA83" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB83" s="5" t="inlineStr"/>
+      <c r="AC83" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090161000163304</t>
         </is>
       </c>
@@ -8619,6 +9173,16 @@
       </c>
       <c r="AA84" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB84" s="5" t="inlineStr">
+        <is>
+          <t>[BAIXA] Industrialização x retorno: Informações complementares citam a industrialização na NF 9015, que é de FABIANO RODRIGUES AMARAL (CFOP 6101); a do cliente é a NF 9016 - informativo, escriturado como está no XML</t>
+        </is>
+      </c>
+      <c r="AC84" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090171000163310</t>
         </is>
       </c>
@@ -8722,6 +9286,16 @@
       </c>
       <c r="AA85" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB85" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC85" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090181000162442</t>
         </is>
       </c>
@@ -8825,6 +9399,16 @@
       </c>
       <c r="AA86" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB86" s="5" t="inlineStr">
+        <is>
+          <t>[MÉDIA] CFOP revenda x produção: 41 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="AC86" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090191000162458</t>
         </is>
       </c>
@@ -8928,6 +9512,16 @@
       </c>
       <c r="AA87" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB87" s="5" t="inlineStr">
+        <is>
+          <t>[ALTA] Industrialização x retorno: Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 6124 de industrialização - o mesmo item foi devolvido também na NF 9026 (6902). Retorno de insumo é 5902/6902; como está, R$ 600.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
+        </is>
+      </c>
+      <c r="AC87" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090201000116651</t>
         </is>
       </c>
@@ -9031,6 +9625,16 @@
       </c>
       <c r="AA88" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB88" s="5" t="inlineStr">
+        <is>
+          <t>[ALTA] Industrialização x retorno: Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 9024 (5902). Retorno de insumo é 5902/6902; como está, R$ 300.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
+        </is>
+      </c>
+      <c r="AC88" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090211000116675</t>
         </is>
       </c>
@@ -9134,6 +9738,12 @@
       </c>
       <c r="AA89" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB89" s="5" t="inlineStr"/>
+      <c r="AC89" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090221000192042</t>
         </is>
       </c>
@@ -9237,6 +9847,12 @@
       </c>
       <c r="AA90" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB90" s="5" t="inlineStr"/>
+      <c r="AC90" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090231000116696</t>
         </is>
       </c>
@@ -9340,6 +9956,12 @@
       </c>
       <c r="AA91" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB91" s="5" t="inlineStr"/>
+      <c r="AC91" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090241000116707</t>
         </is>
       </c>
@@ -9443,6 +10065,12 @@
       </c>
       <c r="AA92" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB92" s="5" t="inlineStr"/>
+      <c r="AC92" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090251000116704</t>
         </is>
       </c>
@@ -9546,6 +10174,12 @@
       </c>
       <c r="AA93" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB93" s="5" t="inlineStr"/>
+      <c r="AC93" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090261000116710</t>
         </is>
       </c>
@@ -9649,6 +10283,12 @@
       </c>
       <c r="AA94" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB94" s="5" t="inlineStr"/>
+      <c r="AC94" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090271000116792</t>
         </is>
       </c>
@@ -9752,6 +10392,12 @@
       </c>
       <c r="AA95" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB95" s="5" t="inlineStr"/>
+      <c r="AC95" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090281000116803</t>
         </is>
       </c>
@@ -9855,6 +10501,12 @@
       </c>
       <c r="AA96" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB96" s="5" t="inlineStr"/>
+      <c r="AC96" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090291000186701</t>
         </is>
       </c>
@@ -9958,6 +10610,12 @@
       </c>
       <c r="AA97" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB97" s="5" t="inlineStr"/>
+      <c r="AC97" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090301000186710</t>
         </is>
       </c>
@@ -10061,6 +10719,12 @@
       </c>
       <c r="AA98" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB98" s="5" t="inlineStr"/>
+      <c r="AC98" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090311000119484</t>
         </is>
       </c>
@@ -10164,6 +10828,12 @@
       </c>
       <c r="AA99" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB99" s="5" t="inlineStr"/>
+      <c r="AC99" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090321000119490</t>
         </is>
       </c>
@@ -10267,6 +10937,12 @@
       </c>
       <c r="AA100" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB100" s="5" t="inlineStr"/>
+      <c r="AC100" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090331000116781</t>
         </is>
       </c>
@@ -10370,6 +11046,12 @@
       </c>
       <c r="AA101" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB101" s="5" t="inlineStr"/>
+      <c r="AC101" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090341000116797</t>
         </is>
       </c>
@@ -10473,6 +11155,12 @@
       </c>
       <c r="AA102" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB102" s="5" t="inlineStr"/>
+      <c r="AC102" s="5" t="inlineStr">
+        <is>
           <t>41260933039048000162550010000090351000187314</t>
         </is>
       </c>
@@ -10575,6 +11263,12 @@
         </is>
       </c>
       <c r="AA103" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB103" s="5" t="inlineStr"/>
+      <c r="AC103" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090361000187320</t>
         </is>
@@ -10657,6 +11351,8 @@
       <c r="Y104" s="8" t="n"/>
       <c r="Z104" s="8" t="n"/>
       <c r="AA104" s="8" t="n"/>
+      <c r="AB104" s="8" t="n"/>
+      <c r="AC104" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -10703,8 +11399,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AA103"/>
-  <conditionalFormatting sqref="A5:AA103">
+  <autoFilter ref="A4:AC103"/>
+  <conditionalFormatting sqref="A5:AC103">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E5="Cancelada"</formula>
     </cfRule>

--- a/Cosmetici/Fiscal/2026-09/Relacao_Saidas_Cosmetici_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Relacao_Saidas_Cosmetici_09-2026.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saídas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Saídas'!$A$4:$AC$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Saídas'!$A$4:$AF$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC109"/>
+  <dimension ref="A1:AF109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -514,12 +514,15 @@
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="9" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
-    <col width="30" customWidth="1" min="26" max="26"/>
-    <col width="30" customWidth="1" min="27" max="27"/>
-    <col width="60" customWidth="1" min="28" max="28"/>
-    <col width="46" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="30" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="30" max="30"/>
+    <col width="60" customWidth="1" min="31" max="31"/>
+    <col width="46" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -654,30 +657,45 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
+          <t>Base IBS/CBS</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>IBS</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>CBS</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
           <t>Total da nota</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Acumulador Domínio</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>Importar no Domínio</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>Conferência XML x Faturamento x Registro (ERP)</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>Análise (informativa - segue o XML)</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>Chave de acesso</t>
         </is>
@@ -726,19 +744,22 @@
       <c r="V5" s="6" t="n"/>
       <c r="W5" s="6" t="n"/>
       <c r="X5" s="6" t="n"/>
-      <c r="Y5" s="5" t="inlineStr"/>
-      <c r="Z5" s="5" t="inlineStr">
-        <is>
-          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
-        </is>
-      </c>
-      <c r="AA5" s="5" t="inlineStr">
-        <is>
-          <t>número inutilizado - fora dos relatórios</t>
-        </is>
-      </c>
+      <c r="Y5" s="6" t="n"/>
+      <c r="Z5" s="6" t="n"/>
+      <c r="AA5" s="6" t="n"/>
       <c r="AB5" s="5" t="inlineStr"/>
       <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
+        </is>
+      </c>
+      <c r="AD5" s="5" t="inlineStr">
+        <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AE5" s="5" t="inlineStr"/>
+      <c r="AF5" s="5" t="inlineStr">
         <is>
           <t>Protocolo 141260351772358</t>
         </is>
@@ -829,29 +850,38 @@
         <v>0</v>
       </c>
       <c r="X6" s="6" t="n">
+        <v>1512.45</v>
+      </c>
+      <c r="Y6" s="6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z6" s="6" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="AA6" s="6" t="n">
         <v>556.05</v>
       </c>
-      <c r="Y6" s="5" t="inlineStr">
+      <c r="AB6" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z6" s="5" t="inlineStr">
+      <c r="AC6" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA6" s="5" t="inlineStr">
+      <c r="AD6" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB6" s="5" t="inlineStr">
+      <c r="AE6" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] Industrialização sem insumo: CFOP 5124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês - informativo (escriturado conforme o XML, CFOP 5124) | [MÉDIA] Diferimento 5124: 5124 para PR com CST 00 (ICMS R$ 108.44) enquanto 35 itens 5124 do mês saíram com diferimento (CST 51). Conferir se o diferimento se aplica a este cliente | [BAIXA] Grupo IPI: 2 it</t>
         </is>
       </c>
-      <c r="AC6" s="5" t="inlineStr">
+      <c r="AF6" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089391000116135</t>
         </is>
@@ -942,25 +972,34 @@
         <v>0</v>
       </c>
       <c r="X7" s="6" t="n">
+        <v>5562.84</v>
+      </c>
+      <c r="Y7" s="6" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="Z7" s="6" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="AA7" s="6" t="n">
         <v>7368</v>
       </c>
-      <c r="Y7" s="5" t="inlineStr">
+      <c r="AB7" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z7" s="5" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>Sim - como CANCELADA (situação 02: valores zerados, só a chave)</t>
         </is>
       </c>
-      <c r="AA7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>cancelada - fora dos dois relatórios (filtro "Situação A")</t>
         </is>
       </c>
-      <c r="AB7" s="5" t="inlineStr"/>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr"/>
+      <c r="AF7" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089401000115920</t>
         </is>
@@ -1051,25 +1090,34 @@
         <v>0</v>
       </c>
       <c r="X8" s="6" t="n">
+        <v>5562.84</v>
+      </c>
+      <c r="Y8" s="6" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="Z8" s="6" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="AA8" s="6" t="n">
         <v>7368</v>
       </c>
-      <c r="Y8" s="5" t="inlineStr">
+      <c r="AB8" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z8" s="5" t="inlineStr">
+      <c r="AC8" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA8" s="5" t="inlineStr">
+      <c r="AD8" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB8" s="5" t="inlineStr"/>
-      <c r="AC8" s="5" t="inlineStr">
+      <c r="AE8" s="5" t="inlineStr"/>
+      <c r="AF8" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089411000115935</t>
         </is>
@@ -1160,25 +1208,34 @@
         <v>0</v>
       </c>
       <c r="X9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="6" t="n">
         <v>1050.6</v>
       </c>
-      <c r="Y9" s="5" t="inlineStr">
+      <c r="AB9" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z9" s="5" t="inlineStr">
+      <c r="AC9" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA9" s="5" t="inlineStr">
+      <c r="AD9" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB9" s="5" t="inlineStr"/>
-      <c r="AC9" s="5" t="inlineStr">
+      <c r="AE9" s="5" t="inlineStr"/>
+      <c r="AF9" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089421000115940</t>
         </is>
@@ -1269,25 +1326,34 @@
         <v>0</v>
       </c>
       <c r="X10" s="6" t="n">
+        <v>4695.6</v>
+      </c>
+      <c r="Y10" s="6" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="Z10" s="6" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="AA10" s="6" t="n">
         <v>5366.4</v>
       </c>
-      <c r="Y10" s="5" t="inlineStr">
+      <c r="AB10" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z10" s="5" t="inlineStr">
+      <c r="AC10" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA10" s="5" t="inlineStr">
+      <c r="AD10" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB10" s="5" t="inlineStr"/>
-      <c r="AC10" s="5" t="inlineStr">
+      <c r="AE10" s="5" t="inlineStr"/>
+      <c r="AF10" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089431000115891</t>
         </is>
@@ -1378,25 +1444,34 @@
         <v>0</v>
       </c>
       <c r="X11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="6" t="n">
         <v>421.2</v>
       </c>
-      <c r="Y11" s="5" t="inlineStr">
+      <c r="AB11" s="5" t="inlineStr">
         <is>
           <t>277 - RETORNO DE MERC NA INDUSTR -</t>
         </is>
       </c>
-      <c r="Z11" s="5" t="inlineStr">
+      <c r="AC11" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA11" s="5" t="inlineStr">
+      <c r="AD11" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB11" s="5" t="inlineStr"/>
-      <c r="AC11" s="5" t="inlineStr">
+      <c r="AE11" s="5" t="inlineStr"/>
+      <c r="AF11" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089441000115902</t>
         </is>
@@ -1487,25 +1562,34 @@
         <v>0</v>
       </c>
       <c r="X12" s="6" t="n">
+        <v>3999.45</v>
+      </c>
+      <c r="Y12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z12" s="6" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="AA12" s="6" t="n">
         <v>4570.8</v>
       </c>
-      <c r="Y12" s="5" t="inlineStr">
+      <c r="AB12" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z12" s="5" t="inlineStr">
+      <c r="AC12" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA12" s="5" t="inlineStr">
+      <c r="AD12" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB12" s="5" t="inlineStr"/>
-      <c r="AC12" s="5" t="inlineStr">
+      <c r="AE12" s="5" t="inlineStr"/>
+      <c r="AF12" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089451000115918</t>
         </is>
@@ -1596,25 +1680,34 @@
         <v>0</v>
       </c>
       <c r="X13" s="6" t="n">
+        <v>2284.59</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Z13" s="6" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="AA13" s="6" t="n">
         <v>2838</v>
       </c>
-      <c r="Y13" s="5" t="inlineStr">
+      <c r="AB13" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z13" s="5" t="inlineStr">
+      <c r="AC13" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA13" s="5" t="inlineStr">
+      <c r="AD13" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB13" s="5" t="inlineStr"/>
-      <c r="AC13" s="5" t="inlineStr">
+      <c r="AE13" s="5" t="inlineStr"/>
+      <c r="AF13" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089461000196494</t>
         </is>
@@ -1705,25 +1798,34 @@
         <v>0</v>
       </c>
       <c r="X14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="6" t="n">
         <v>222.6</v>
       </c>
-      <c r="Y14" s="5" t="inlineStr">
+      <c r="AB14" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z14" s="5" t="inlineStr">
+      <c r="AC14" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA14" s="5" t="inlineStr">
+      <c r="AD14" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB14" s="5" t="inlineStr"/>
-      <c r="AC14" s="5" t="inlineStr">
+      <c r="AE14" s="5" t="inlineStr"/>
+      <c r="AF14" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089471000196505</t>
         </is>
@@ -1772,19 +1874,22 @@
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
       <c r="X15" s="6" t="n"/>
-      <c r="Y15" s="5" t="inlineStr"/>
-      <c r="Z15" s="5" t="inlineStr">
-        <is>
-          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
-        </is>
-      </c>
-      <c r="AA15" s="5" t="inlineStr">
-        <is>
-          <t>número inutilizado - fora dos relatórios</t>
-        </is>
-      </c>
+      <c r="Y15" s="6" t="n"/>
+      <c r="Z15" s="6" t="n"/>
+      <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="5" t="inlineStr"/>
       <c r="AC15" s="5" t="inlineStr">
+        <is>
+          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
+        </is>
+      </c>
+      <c r="AD15" s="5" t="inlineStr">
+        <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AE15" s="5" t="inlineStr"/>
+      <c r="AF15" s="5" t="inlineStr">
         <is>
           <t>Protocolo 141260353599070</t>
         </is>
@@ -1875,25 +1980,34 @@
         <v>0</v>
       </c>
       <c r="X16" s="6" t="n">
+        <v>1637.37</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z16" s="6" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="AA16" s="6" t="n">
         <v>2034</v>
       </c>
-      <c r="Y16" s="5" t="inlineStr">
+      <c r="AB16" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z16" s="5" t="inlineStr">
+      <c r="AC16" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA16" s="5" t="inlineStr">
+      <c r="AD16" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB16" s="5" t="inlineStr"/>
-      <c r="AC16" s="5" t="inlineStr">
+      <c r="AE16" s="5" t="inlineStr"/>
+      <c r="AF16" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089491000204197</t>
         </is>
@@ -1984,25 +2098,34 @@
         <v>0</v>
       </c>
       <c r="X17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="6" t="n">
         <v>159</v>
       </c>
-      <c r="Y17" s="5" t="inlineStr">
+      <c r="AB17" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z17" s="5" t="inlineStr">
+      <c r="AC17" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA17" s="5" t="inlineStr">
+      <c r="AD17" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB17" s="5" t="inlineStr"/>
-      <c r="AC17" s="5" t="inlineStr">
+      <c r="AE17" s="5" t="inlineStr"/>
+      <c r="AF17" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089501000204201</t>
         </is>
@@ -2051,19 +2174,22 @@
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
       <c r="X18" s="6" t="n"/>
-      <c r="Y18" s="5" t="inlineStr"/>
-      <c r="Z18" s="5" t="inlineStr">
-        <is>
-          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
-        </is>
-      </c>
-      <c r="AA18" s="5" t="inlineStr">
-        <is>
-          <t>número inutilizado - fora dos relatórios</t>
-        </is>
-      </c>
+      <c r="Y18" s="6" t="n"/>
+      <c r="Z18" s="6" t="n"/>
+      <c r="AA18" s="6" t="n"/>
       <c r="AB18" s="5" t="inlineStr"/>
       <c r="AC18" s="5" t="inlineStr">
+        <is>
+          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
+        </is>
+      </c>
+      <c r="AD18" s="5" t="inlineStr">
+        <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AE18" s="5" t="inlineStr"/>
+      <c r="AF18" s="5" t="inlineStr">
         <is>
           <t>Protocolo 141260353639120</t>
         </is>
@@ -2154,25 +2280,34 @@
         <v>0</v>
       </c>
       <c r="X19" s="6" t="n">
+        <v>4761.89</v>
+      </c>
+      <c r="Y19" s="6" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Z19" s="6" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="AA19" s="6" t="n">
         <v>6307.1</v>
       </c>
-      <c r="Y19" s="5" t="inlineStr">
+      <c r="AB19" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z19" s="5" t="inlineStr">
+      <c r="AC19" s="5" t="inlineStr">
         <is>
           <t>Sim - como CANCELADA (situação 02: valores zerados, só a chave)</t>
         </is>
       </c>
-      <c r="AA19" s="5" t="inlineStr">
+      <c r="AD19" s="5" t="inlineStr">
         <is>
           <t>cancelada - fora dos dois relatórios (filtro "Situação A")</t>
         </is>
       </c>
-      <c r="AB19" s="5" t="inlineStr"/>
-      <c r="AC19" s="5" t="inlineStr">
+      <c r="AE19" s="5" t="inlineStr"/>
+      <c r="AF19" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089521000162996</t>
         </is>
@@ -2263,25 +2398,34 @@
         <v>0</v>
       </c>
       <c r="X20" s="6" t="n">
+        <v>4761.89</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Z20" s="6" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="AA20" s="6" t="n">
         <v>6307.1</v>
       </c>
-      <c r="Y20" s="5" t="inlineStr">
+      <c r="AB20" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z20" s="5" t="inlineStr">
+      <c r="AC20" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA20" s="5" t="inlineStr">
+      <c r="AD20" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB20" s="5" t="inlineStr"/>
-      <c r="AC20" s="5" t="inlineStr">
+      <c r="AE20" s="5" t="inlineStr"/>
+      <c r="AF20" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089531000163000</t>
         </is>
@@ -2372,25 +2516,34 @@
         <v>0</v>
       </c>
       <c r="X21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="6" t="n">
         <v>614.16</v>
       </c>
-      <c r="Y21" s="5" t="inlineStr">
+      <c r="AB21" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z21" s="5" t="inlineStr">
+      <c r="AC21" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA21" s="5" t="inlineStr">
+      <c r="AD21" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB21" s="5" t="inlineStr"/>
-      <c r="AC21" s="5" t="inlineStr">
+      <c r="AE21" s="5" t="inlineStr"/>
+      <c r="AF21" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089541000163016</t>
         </is>
@@ -2481,25 +2634,34 @@
         <v>0</v>
       </c>
       <c r="X22" s="6" t="n">
+        <v>2103.71</v>
+      </c>
+      <c r="Y22" s="6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z22" s="6" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="AA22" s="6" t="n">
         <v>4050.02</v>
       </c>
-      <c r="Y22" s="5" t="inlineStr">
+      <c r="AB22" s="5" t="inlineStr">
         <is>
           <t>202 - VENDA C/ ST - DENTRO DO ESTA</t>
         </is>
       </c>
-      <c r="Z22" s="5" t="inlineStr">
+      <c r="AC22" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA22" s="5" t="inlineStr">
+      <c r="AD22" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB22" s="5" t="inlineStr"/>
-      <c r="AC22" s="5" t="inlineStr">
+      <c r="AE22" s="5" t="inlineStr"/>
+      <c r="AF22" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089551000161819</t>
         </is>
@@ -2548,19 +2710,22 @@
       <c r="V23" s="6" t="n"/>
       <c r="W23" s="6" t="n"/>
       <c r="X23" s="6" t="n"/>
-      <c r="Y23" s="5" t="inlineStr"/>
-      <c r="Z23" s="5" t="inlineStr">
-        <is>
-          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
-        </is>
-      </c>
-      <c r="AA23" s="5" t="inlineStr">
-        <is>
-          <t>número inutilizado - fora dos relatórios</t>
-        </is>
-      </c>
+      <c r="Y23" s="6" t="n"/>
+      <c r="Z23" s="6" t="n"/>
+      <c r="AA23" s="6" t="n"/>
       <c r="AB23" s="5" t="inlineStr"/>
       <c r="AC23" s="5" t="inlineStr">
+        <is>
+          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
+        </is>
+      </c>
+      <c r="AD23" s="5" t="inlineStr">
+        <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AE23" s="5" t="inlineStr"/>
+      <c r="AF23" s="5" t="inlineStr">
         <is>
           <t>Protocolo 141260355633030</t>
         </is>
@@ -2651,25 +2816,34 @@
         <v>0</v>
       </c>
       <c r="X24" s="6" t="n">
+        <v>1543.5</v>
+      </c>
+      <c r="Y24" s="6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z24" s="6" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AA24" s="6" t="n">
         <v>1764</v>
       </c>
-      <c r="Y24" s="5" t="inlineStr">
+      <c r="AB24" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z24" s="5" t="inlineStr">
+      <c r="AC24" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA24" s="5" t="inlineStr">
+      <c r="AD24" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB24" s="5" t="inlineStr"/>
-      <c r="AC24" s="5" t="inlineStr">
+      <c r="AE24" s="5" t="inlineStr"/>
+      <c r="AF24" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089571000162992</t>
         </is>
@@ -2760,25 +2934,34 @@
         <v>0</v>
       </c>
       <c r="X25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="6" t="n">
         <v>182.4</v>
       </c>
-      <c r="Y25" s="5" t="inlineStr">
+      <c r="AB25" s="5" t="inlineStr">
         <is>
           <t>277 - RETORNO DE MERC NA INDUSTR -</t>
         </is>
       </c>
-      <c r="Z25" s="5" t="inlineStr">
+      <c r="AC25" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA25" s="5" t="inlineStr">
+      <c r="AD25" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB25" s="5" t="inlineStr"/>
-      <c r="AC25" s="5" t="inlineStr">
+      <c r="AE25" s="5" t="inlineStr"/>
+      <c r="AF25" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089581000163007</t>
         </is>
@@ -2869,25 +3052,34 @@
         <v>0</v>
       </c>
       <c r="X26" s="6" t="n">
+        <v>4389</v>
+      </c>
+      <c r="Y26" s="6" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="Z26" s="6" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AA26" s="6" t="n">
         <v>5016</v>
       </c>
-      <c r="Y26" s="5" t="inlineStr">
+      <c r="AB26" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z26" s="5" t="inlineStr">
+      <c r="AC26" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA26" s="5" t="inlineStr">
+      <c r="AD26" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB26" s="5" t="inlineStr"/>
-      <c r="AC26" s="5" t="inlineStr">
+      <c r="AE26" s="5" t="inlineStr"/>
+      <c r="AF26" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089591000156962</t>
         </is>
@@ -2978,25 +3170,34 @@
         <v>0</v>
       </c>
       <c r="X27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="6" t="n">
         <v>266.4</v>
       </c>
-      <c r="Y27" s="5" t="inlineStr">
+      <c r="AB27" s="5" t="inlineStr">
         <is>
           <t>277 - RETORNO DE MERC NA INDUSTR -</t>
         </is>
       </c>
-      <c r="Z27" s="5" t="inlineStr">
+      <c r="AC27" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA27" s="5" t="inlineStr">
+      <c r="AD27" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB27" s="5" t="inlineStr"/>
-      <c r="AC27" s="5" t="inlineStr">
+      <c r="AE27" s="5" t="inlineStr"/>
+      <c r="AF27" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089601000156971</t>
         </is>
@@ -3087,25 +3288,34 @@
         <v>0</v>
       </c>
       <c r="X28" s="6" t="n">
+        <v>4892.4</v>
+      </c>
+      <c r="Y28" s="6" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="Z28" s="6" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="AA28" s="6" t="n">
         <v>1620</v>
       </c>
-      <c r="Y28" s="5" t="inlineStr">
+      <c r="AB28" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z28" s="5" t="inlineStr">
+      <c r="AC28" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA28" s="5" t="inlineStr">
+      <c r="AD28" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB28" s="5" t="inlineStr"/>
-      <c r="AC28" s="5" t="inlineStr">
+      <c r="AE28" s="5" t="inlineStr"/>
+      <c r="AF28" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089611000197772</t>
         </is>
@@ -3196,25 +3406,34 @@
         <v>0</v>
       </c>
       <c r="X29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="6" t="n">
         <v>1805.6</v>
       </c>
-      <c r="Y29" s="5" t="inlineStr">
+      <c r="AB29" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z29" s="5" t="inlineStr">
+      <c r="AC29" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA29" s="5" t="inlineStr">
+      <c r="AD29" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB29" s="5" t="inlineStr"/>
-      <c r="AC29" s="5" t="inlineStr">
+      <c r="AE29" s="5" t="inlineStr"/>
+      <c r="AF29" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089621000197788</t>
         </is>
@@ -3305,25 +3524,34 @@
         <v>0</v>
       </c>
       <c r="X30" s="6" t="n">
+        <v>2414.49</v>
+      </c>
+      <c r="Y30" s="6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Z30" s="6" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="AA30" s="6" t="n">
         <v>1379.7</v>
       </c>
-      <c r="Y30" s="5" t="inlineStr">
+      <c r="AB30" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z30" s="5" t="inlineStr">
+      <c r="AC30" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA30" s="5" t="inlineStr">
+      <c r="AD30" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB30" s="5" t="inlineStr"/>
-      <c r="AC30" s="5" t="inlineStr">
+      <c r="AE30" s="5" t="inlineStr"/>
+      <c r="AF30" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089631000118800</t>
         </is>
@@ -3414,25 +3642,34 @@
         <v>0</v>
       </c>
       <c r="X31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="6" t="n">
         <v>417.6</v>
       </c>
-      <c r="Y31" s="5" t="inlineStr">
+      <c r="AB31" s="5" t="inlineStr">
         <is>
           <t>277 - RETORNO DE MERC NA INDUSTR -</t>
         </is>
       </c>
-      <c r="Z31" s="5" t="inlineStr">
+      <c r="AC31" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA31" s="5" t="inlineStr">
+      <c r="AD31" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB31" s="5" t="inlineStr"/>
-      <c r="AC31" s="5" t="inlineStr">
+      <c r="AE31" s="5" t="inlineStr"/>
+      <c r="AF31" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089641000118815</t>
         </is>
@@ -3481,19 +3718,22 @@
       <c r="V32" s="6" t="n"/>
       <c r="W32" s="6" t="n"/>
       <c r="X32" s="6" t="n"/>
-      <c r="Y32" s="5" t="inlineStr"/>
-      <c r="Z32" s="5" t="inlineStr">
-        <is>
-          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
-        </is>
-      </c>
-      <c r="AA32" s="5" t="inlineStr">
-        <is>
-          <t>número inutilizado - fora dos relatórios</t>
-        </is>
-      </c>
+      <c r="Y32" s="6" t="n"/>
+      <c r="Z32" s="6" t="n"/>
+      <c r="AA32" s="6" t="n"/>
       <c r="AB32" s="5" t="inlineStr"/>
       <c r="AC32" s="5" t="inlineStr">
+        <is>
+          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
+        </is>
+      </c>
+      <c r="AD32" s="5" t="inlineStr">
+        <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AE32" s="5" t="inlineStr"/>
+      <c r="AF32" s="5" t="inlineStr">
         <is>
           <t>Protocolo 141260363749669</t>
         </is>
@@ -3584,25 +3824,34 @@
         <v>40.06</v>
       </c>
       <c r="X33" s="6" t="n">
+        <v>2520.49</v>
+      </c>
+      <c r="Y33" s="6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Z33" s="6" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="AA33" s="6" t="n">
         <v>667.6799999999999</v>
       </c>
-      <c r="Y33" s="5" t="inlineStr">
+      <c r="AB33" s="5" t="inlineStr">
         <is>
           <t>201 - VENDA S/ ST - FORA DO ESTADO</t>
         </is>
       </c>
-      <c r="Z33" s="5" t="inlineStr">
+      <c r="AC33" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA33" s="5" t="inlineStr">
+      <c r="AD33" s="5" t="inlineStr">
         <is>
           <t>Registro: UF PR x XML SP</t>
         </is>
       </c>
-      <c r="AB33" s="5" t="inlineStr"/>
-      <c r="AC33" s="5" t="inlineStr">
+      <c r="AE33" s="5" t="inlineStr"/>
+      <c r="AF33" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089661000161928</t>
         </is>
@@ -3693,29 +3942,38 @@
         <v>22.22</v>
       </c>
       <c r="X34" s="6" t="n">
+        <v>239.06</v>
+      </c>
+      <c r="Y34" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z34" s="6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA34" s="6" t="n">
         <v>370.33</v>
       </c>
-      <c r="Y34" s="5" t="inlineStr">
+      <c r="AB34" s="5" t="inlineStr">
         <is>
           <t>201 - VENDA S/ ST - FORA DO ESTADO</t>
         </is>
       </c>
-      <c r="Z34" s="5" t="inlineStr">
+      <c r="AC34" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA34" s="5" t="inlineStr">
+      <c r="AD34" s="5" t="inlineStr">
         <is>
           <t>Registro: UF PR x XML SP</t>
         </is>
       </c>
-      <c r="AB34" s="5" t="inlineStr">
+      <c r="AE34" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 6102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC34" s="5" t="inlineStr">
+      <c r="AF34" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089671000161933</t>
         </is>
@@ -3806,25 +4064,34 @@
         <v>0</v>
       </c>
       <c r="X35" s="6" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="Y35" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z35" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AA35" s="6" t="n">
         <v>157.2</v>
       </c>
-      <c r="Y35" s="5" t="inlineStr">
+      <c r="AB35" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z35" s="5" t="inlineStr">
+      <c r="AC35" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA35" s="5" t="inlineStr">
+      <c r="AD35" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB35" s="5" t="inlineStr"/>
-      <c r="AC35" s="5" t="inlineStr">
+      <c r="AE35" s="5" t="inlineStr"/>
+      <c r="AF35" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089681000161949</t>
         </is>
@@ -3915,29 +4182,38 @@
         <v>0</v>
       </c>
       <c r="X36" s="6" t="n">
+        <v>463.27</v>
+      </c>
+      <c r="Y36" s="6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="Z36" s="6" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AA36" s="6" t="n">
         <v>811.99</v>
       </c>
-      <c r="Y36" s="5" t="inlineStr">
+      <c r="AB36" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z36" s="5" t="inlineStr">
+      <c r="AC36" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA36" s="5" t="inlineStr">
+      <c r="AD36" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB36" s="5" t="inlineStr">
+      <c r="AE36" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC36" s="5" t="inlineStr">
+      <c r="AF36" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089691000161954</t>
         </is>
@@ -4028,25 +4304,34 @@
         <v>0</v>
       </c>
       <c r="X37" s="6" t="n">
+        <v>2706.39</v>
+      </c>
+      <c r="Y37" s="6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z37" s="6" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="AA37" s="6" t="n">
         <v>995.01</v>
       </c>
-      <c r="Y37" s="5" t="inlineStr">
+      <c r="AB37" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z37" s="5" t="inlineStr">
+      <c r="AC37" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA37" s="5" t="inlineStr">
+      <c r="AD37" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB37" s="5" t="inlineStr"/>
-      <c r="AC37" s="5" t="inlineStr">
+      <c r="AE37" s="5" t="inlineStr"/>
+      <c r="AF37" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089701000116445</t>
         </is>
@@ -4137,25 +4422,34 @@
         <v>0</v>
       </c>
       <c r="X38" s="6" t="n">
+        <v>2505.09</v>
+      </c>
+      <c r="Y38" s="6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Z38" s="6" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="AA38" s="6" t="n">
         <v>3318</v>
       </c>
-      <c r="Y38" s="5" t="inlineStr">
+      <c r="AB38" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z38" s="5" t="inlineStr">
+      <c r="AC38" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA38" s="5" t="inlineStr">
+      <c r="AD38" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB38" s="5" t="inlineStr"/>
-      <c r="AC38" s="5" t="inlineStr">
+      <c r="AE38" s="5" t="inlineStr"/>
+      <c r="AF38" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089711000207812</t>
         </is>
@@ -4246,29 +4540,38 @@
         <v>0</v>
       </c>
       <c r="X39" s="6" t="n">
+        <v>3259.86</v>
+      </c>
+      <c r="Y39" s="6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="Z39" s="6" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="AA39" s="6" t="n">
         <v>4049.52</v>
       </c>
-      <c r="Y39" s="5" t="inlineStr">
+      <c r="AB39" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z39" s="5" t="inlineStr">
+      <c r="AC39" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA39" s="5" t="inlineStr">
+      <c r="AD39" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB39" s="5" t="inlineStr">
+      <c r="AE39" s="5" t="inlineStr">
         <is>
           <t>[BAIXA] Grupo IPI: 2 item(ns) de produto (CFOP 6124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
         </is>
       </c>
-      <c r="AC39" s="5" t="inlineStr">
+      <c r="AF39" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089731000116625</t>
         </is>
@@ -4359,25 +4662,34 @@
         <v>0</v>
       </c>
       <c r="X40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="6" t="n">
         <v>299.52</v>
       </c>
-      <c r="Y40" s="5" t="inlineStr">
+      <c r="AB40" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z40" s="5" t="inlineStr">
+      <c r="AC40" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA40" s="5" t="inlineStr">
+      <c r="AD40" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB40" s="5" t="inlineStr"/>
-      <c r="AC40" s="5" t="inlineStr">
+      <c r="AE40" s="5" t="inlineStr"/>
+      <c r="AF40" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089741000116630</t>
         </is>
@@ -4468,25 +4780,34 @@
         <v>0</v>
       </c>
       <c r="X41" s="6" t="n">
+        <v>3585.74</v>
+      </c>
+      <c r="Y41" s="6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Z41" s="6" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="AA41" s="6" t="n">
         <v>4098</v>
       </c>
-      <c r="Y41" s="5" t="inlineStr">
+      <c r="AB41" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z41" s="5" t="inlineStr">
+      <c r="AC41" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA41" s="5" t="inlineStr">
+      <c r="AD41" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB41" s="5" t="inlineStr"/>
-      <c r="AC41" s="5" t="inlineStr">
+      <c r="AE41" s="5" t="inlineStr"/>
+      <c r="AF41" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089751000191575</t>
         </is>
@@ -4577,25 +4898,34 @@
         <v>0</v>
       </c>
       <c r="X42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="6" t="n">
         <v>588</v>
       </c>
-      <c r="Y42" s="5" t="inlineStr">
+      <c r="AB42" s="5" t="inlineStr">
         <is>
           <t>277 - RETORNO DE MERC NA INDUSTR -</t>
         </is>
       </c>
-      <c r="Z42" s="5" t="inlineStr">
+      <c r="AC42" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA42" s="5" t="inlineStr">
+      <c r="AD42" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB42" s="5" t="inlineStr"/>
-      <c r="AC42" s="5" t="inlineStr">
+      <c r="AE42" s="5" t="inlineStr"/>
+      <c r="AF42" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089761000191580</t>
         </is>
@@ -4686,25 +5016,34 @@
         <v>0</v>
       </c>
       <c r="X43" s="6" t="n">
+        <v>2397.5</v>
+      </c>
+      <c r="Y43" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z43" s="6" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="AA43" s="6" t="n">
         <v>2740</v>
       </c>
-      <c r="Y43" s="5" t="inlineStr">
+      <c r="AB43" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z43" s="5" t="inlineStr">
+      <c r="AC43" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA43" s="5" t="inlineStr">
+      <c r="AD43" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB43" s="5" t="inlineStr"/>
-      <c r="AC43" s="5" t="inlineStr">
+      <c r="AE43" s="5" t="inlineStr"/>
+      <c r="AF43" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089771000191596</t>
         </is>
@@ -4795,29 +5134,38 @@
         <v>0</v>
       </c>
       <c r="X44" s="6" t="n">
+        <v>969.09</v>
+      </c>
+      <c r="Y44" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="Z44" s="6" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="AA44" s="6" t="n">
         <v>1698.59</v>
       </c>
-      <c r="Y44" s="5" t="inlineStr">
+      <c r="AB44" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z44" s="5" t="inlineStr">
+      <c r="AC44" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA44" s="5" t="inlineStr">
+      <c r="AD44" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB44" s="5" t="inlineStr">
+      <c r="AE44" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 9 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC44" s="5" t="inlineStr">
+      <c r="AF44" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089781000162046</t>
         </is>
@@ -4866,19 +5214,22 @@
       <c r="V45" s="6" t="n"/>
       <c r="W45" s="6" t="n"/>
       <c r="X45" s="6" t="n"/>
-      <c r="Y45" s="5" t="inlineStr"/>
-      <c r="Z45" s="5" t="inlineStr">
-        <is>
-          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
-        </is>
-      </c>
-      <c r="AA45" s="5" t="inlineStr">
-        <is>
-          <t>número inutilizado - fora dos relatórios</t>
-        </is>
-      </c>
+      <c r="Y45" s="6" t="n"/>
+      <c r="Z45" s="6" t="n"/>
+      <c r="AA45" s="6" t="n"/>
       <c r="AB45" s="5" t="inlineStr"/>
       <c r="AC45" s="5" t="inlineStr">
+        <is>
+          <t>Sim - como INUTILIZADA (situação 05, só o número)</t>
+        </is>
+      </c>
+      <c r="AD45" s="5" t="inlineStr">
+        <is>
+          <t>número inutilizado - fora dos relatórios</t>
+        </is>
+      </c>
+      <c r="AE45" s="5" t="inlineStr"/>
+      <c r="AF45" s="5" t="inlineStr">
         <is>
           <t>Protocolo 141260375536433</t>
         </is>
@@ -4969,29 +5320,38 @@
         <v>0</v>
       </c>
       <c r="X46" s="6" t="n">
+        <v>3298.89</v>
+      </c>
+      <c r="Y46" s="6" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="Z46" s="6" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="AA46" s="6" t="n">
         <v>4098</v>
       </c>
-      <c r="Y46" s="5" t="inlineStr">
+      <c r="AB46" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z46" s="5" t="inlineStr">
+      <c r="AC46" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA46" s="5" t="inlineStr">
+      <c r="AD46" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB46" s="5" t="inlineStr">
+      <c r="AE46" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] Industrialização sem insumo: CFOP 6124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês - informativo (escriturado conforme o XML, CFOP 6124)</t>
         </is>
       </c>
-      <c r="AC46" s="5" t="inlineStr">
+      <c r="AF46" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089791000217000</t>
         </is>
@@ -5082,29 +5442,38 @@
         <v>0</v>
       </c>
       <c r="X47" s="6" t="n">
+        <v>10812.56</v>
+      </c>
+      <c r="Y47" s="6" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="Z47" s="6" t="n">
+        <v>97.31</v>
+      </c>
+      <c r="AA47" s="6" t="n">
         <v>17771.69</v>
       </c>
-      <c r="Y47" s="5" t="inlineStr">
+      <c r="AB47" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z47" s="5" t="inlineStr">
+      <c r="AC47" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA47" s="5" t="inlineStr">
+      <c r="AD47" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB47" s="5" t="inlineStr">
+      <c r="AE47" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 19 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS" | [BAIXA] Grupo IPI: 3 item(ns) de produto (CFOP 5102) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
         </is>
       </c>
-      <c r="AC47" s="5" t="inlineStr">
+      <c r="AF47" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089801000162060</t>
         </is>
@@ -5195,29 +5564,38 @@
         <v>0</v>
       </c>
       <c r="X48" s="6" t="n">
+        <v>965.09</v>
+      </c>
+      <c r="Y48" s="6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="Z48" s="6" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="AA48" s="6" t="n">
         <v>1691.57</v>
       </c>
-      <c r="Y48" s="5" t="inlineStr">
+      <c r="AB48" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z48" s="5" t="inlineStr">
+      <c r="AC48" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA48" s="5" t="inlineStr">
+      <c r="AD48" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB48" s="5" t="inlineStr">
+      <c r="AE48" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC48" s="5" t="inlineStr">
+      <c r="AF48" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089811000162076</t>
         </is>
@@ -5308,29 +5686,38 @@
         <v>0</v>
       </c>
       <c r="X49" s="6" t="n">
+        <v>3937.47</v>
+      </c>
+      <c r="Y49" s="6" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Z49" s="6" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="AA49" s="6" t="n">
         <v>6901.45</v>
       </c>
-      <c r="Y49" s="5" t="inlineStr">
+      <c r="AB49" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z49" s="5" t="inlineStr">
+      <c r="AC49" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA49" s="5" t="inlineStr">
+      <c r="AD49" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB49" s="5" t="inlineStr">
+      <c r="AE49" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC49" s="5" t="inlineStr">
+      <c r="AF49" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089821000162081</t>
         </is>
@@ -5421,25 +5808,34 @@
         <v>0</v>
       </c>
       <c r="X50" s="6" t="n">
+        <v>3115.35</v>
+      </c>
+      <c r="Y50" s="6" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Z50" s="6" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="AA50" s="6" t="n">
         <v>967.5</v>
       </c>
-      <c r="Y50" s="5" t="inlineStr">
+      <c r="AB50" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z50" s="5" t="inlineStr">
+      <c r="AC50" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA50" s="5" t="inlineStr">
+      <c r="AD50" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB50" s="5" t="inlineStr"/>
-      <c r="AC50" s="5" t="inlineStr">
+      <c r="AE50" s="5" t="inlineStr"/>
+      <c r="AF50" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089831000120041</t>
         </is>
@@ -5530,25 +5926,34 @@
         <v>0</v>
       </c>
       <c r="X51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="6" t="n">
         <v>334.8</v>
       </c>
-      <c r="Y51" s="5" t="inlineStr">
+      <c r="AB51" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z51" s="5" t="inlineStr">
+      <c r="AC51" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA51" s="5" t="inlineStr">
+      <c r="AD51" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB51" s="5" t="inlineStr"/>
-      <c r="AC51" s="5" t="inlineStr">
+      <c r="AE51" s="5" t="inlineStr"/>
+      <c r="AF51" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089841000120057</t>
         </is>
@@ -5639,25 +6044,34 @@
         <v>0</v>
       </c>
       <c r="X52" s="6" t="n">
+        <v>303.51</v>
+      </c>
+      <c r="Y52" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z52" s="6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA52" s="6" t="n">
         <v>402</v>
       </c>
-      <c r="Y52" s="5" t="inlineStr">
+      <c r="AB52" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z52" s="5" t="inlineStr">
+      <c r="AC52" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA52" s="5" t="inlineStr">
+      <c r="AD52" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB52" s="5" t="inlineStr"/>
-      <c r="AC52" s="5" t="inlineStr">
+      <c r="AE52" s="5" t="inlineStr"/>
+      <c r="AF52" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089851000116375</t>
         </is>
@@ -5748,25 +6162,34 @@
         <v>0</v>
       </c>
       <c r="X53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="6" t="n">
         <v>101.05</v>
       </c>
-      <c r="Y53" s="5" t="inlineStr">
+      <c r="AB53" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z53" s="5" t="inlineStr">
+      <c r="AC53" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA53" s="5" t="inlineStr">
+      <c r="AD53" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB53" s="5" t="inlineStr"/>
-      <c r="AC53" s="5" t="inlineStr">
+      <c r="AE53" s="5" t="inlineStr"/>
+      <c r="AF53" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089861000116380</t>
         </is>
@@ -5857,25 +6280,34 @@
         <v>0</v>
       </c>
       <c r="X54" s="6" t="n">
+        <v>1116.85</v>
+      </c>
+      <c r="Y54" s="6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z54" s="6" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="AA54" s="6" t="n">
         <v>1479.27</v>
       </c>
-      <c r="Y54" s="5" t="inlineStr">
+      <c r="AB54" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z54" s="5" t="inlineStr">
+      <c r="AC54" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA54" s="5" t="inlineStr">
+      <c r="AD54" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB54" s="5" t="inlineStr"/>
-      <c r="AC54" s="5" t="inlineStr">
+      <c r="AE54" s="5" t="inlineStr"/>
+      <c r="AF54" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089871000126294</t>
         </is>
@@ -5966,25 +6398,34 @@
         <v>0</v>
       </c>
       <c r="X55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="6" t="n">
         <v>41.76</v>
       </c>
-      <c r="Y55" s="5" t="inlineStr">
+      <c r="AB55" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z55" s="5" t="inlineStr">
+      <c r="AC55" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA55" s="5" t="inlineStr">
+      <c r="AD55" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB55" s="5" t="inlineStr"/>
-      <c r="AC55" s="5" t="inlineStr">
+      <c r="AE55" s="5" t="inlineStr"/>
+      <c r="AF55" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089881000126305</t>
         </is>
@@ -6075,29 +6516,38 @@
         <v>0</v>
       </c>
       <c r="X56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="Y56" s="5" t="inlineStr">
+      <c r="AB56" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z56" s="5" t="inlineStr">
+      <c r="AC56" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA56" s="5" t="inlineStr">
+      <c r="AD56" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB56" s="5" t="inlineStr">
+      <c r="AE56" s="5" t="inlineStr">
         <is>
           <t>[ALTA] Industrialização x retorno: Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 8993 (5902). Retorno de insumo é 5902/6902; como está, R$ 600.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
         </is>
       </c>
-      <c r="AC56" s="5" t="inlineStr">
+      <c r="AF56" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089891000116358</t>
         </is>
@@ -6188,25 +6638,34 @@
         <v>0</v>
       </c>
       <c r="X57" s="6" t="n">
+        <v>825.13</v>
+      </c>
+      <c r="Y57" s="6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="Z57" s="6" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="AA57" s="6" t="n">
         <v>1092.89</v>
       </c>
-      <c r="Y57" s="5" t="inlineStr">
+      <c r="AB57" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z57" s="5" t="inlineStr">
+      <c r="AC57" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA57" s="5" t="inlineStr">
+      <c r="AD57" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB57" s="5" t="inlineStr"/>
-      <c r="AC57" s="5" t="inlineStr">
+      <c r="AE57" s="5" t="inlineStr"/>
+      <c r="AF57" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089901000207184</t>
         </is>
@@ -6297,25 +6756,34 @@
         <v>0</v>
       </c>
       <c r="X58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="6" t="n">
         <v>32.64</v>
       </c>
-      <c r="Y58" s="5" t="inlineStr">
+      <c r="AB58" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z58" s="5" t="inlineStr">
+      <c r="AC58" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA58" s="5" t="inlineStr">
+      <c r="AD58" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB58" s="5" t="inlineStr"/>
-      <c r="AC58" s="5" t="inlineStr">
+      <c r="AE58" s="5" t="inlineStr"/>
+      <c r="AF58" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089911000207190</t>
         </is>
@@ -6406,25 +6874,34 @@
         <v>0</v>
       </c>
       <c r="X59" s="6" t="n">
+        <v>3325</v>
+      </c>
+      <c r="Y59" s="6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Z59" s="6" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="AA59" s="6" t="n">
         <v>3800</v>
       </c>
-      <c r="Y59" s="5" t="inlineStr">
+      <c r="AB59" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z59" s="5" t="inlineStr">
+      <c r="AC59" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA59" s="5" t="inlineStr">
+      <c r="AD59" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB59" s="5" t="inlineStr"/>
-      <c r="AC59" s="5" t="inlineStr">
+      <c r="AE59" s="5" t="inlineStr"/>
+      <c r="AF59" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089921000116388</t>
         </is>
@@ -6515,25 +6992,34 @@
         <v>0</v>
       </c>
       <c r="X60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="Y60" s="5" t="inlineStr">
+      <c r="AB60" s="5" t="inlineStr">
         <is>
           <t>277 - RETORNO DE MERC NA INDUSTR -</t>
         </is>
       </c>
-      <c r="Z60" s="5" t="inlineStr">
+      <c r="AC60" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA60" s="5" t="inlineStr">
+      <c r="AD60" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB60" s="5" t="inlineStr"/>
-      <c r="AC60" s="5" t="inlineStr">
+      <c r="AE60" s="5" t="inlineStr"/>
+      <c r="AF60" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089931000116393</t>
         </is>
@@ -6624,25 +7110,34 @@
         <v>0</v>
       </c>
       <c r="X61" s="6" t="n">
+        <v>1019.25</v>
+      </c>
+      <c r="Y61" s="6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z61" s="6" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AA61" s="6" t="n">
         <v>1350</v>
       </c>
-      <c r="Y61" s="5" t="inlineStr">
+      <c r="AB61" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z61" s="5" t="inlineStr">
+      <c r="AC61" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA61" s="5" t="inlineStr">
+      <c r="AD61" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB61" s="5" t="inlineStr"/>
-      <c r="AC61" s="5" t="inlineStr">
+      <c r="AE61" s="5" t="inlineStr"/>
+      <c r="AF61" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089941000166452</t>
         </is>
@@ -6733,25 +7228,34 @@
         <v>0</v>
       </c>
       <c r="X62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="6" t="n">
         <v>73.8</v>
       </c>
-      <c r="Y62" s="5" t="inlineStr">
+      <c r="AB62" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z62" s="5" t="inlineStr">
+      <c r="AC62" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA62" s="5" t="inlineStr">
+      <c r="AD62" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB62" s="5" t="inlineStr"/>
-      <c r="AC62" s="5" t="inlineStr">
+      <c r="AE62" s="5" t="inlineStr"/>
+      <c r="AF62" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089951000166468</t>
         </is>
@@ -6842,25 +7346,34 @@
         <v>0</v>
       </c>
       <c r="X63" s="6" t="n">
+        <v>1887.52</v>
+      </c>
+      <c r="Y63" s="6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z63" s="6" t="n">
+        <v>16.97</v>
+      </c>
+      <c r="AA63" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="Y63" s="5" t="inlineStr">
+      <c r="AB63" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z63" s="5" t="inlineStr">
+      <c r="AC63" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA63" s="5" t="inlineStr">
+      <c r="AD63" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB63" s="5" t="inlineStr"/>
-      <c r="AC63" s="5" t="inlineStr">
+      <c r="AE63" s="5" t="inlineStr"/>
+      <c r="AF63" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089961000197247</t>
         </is>
@@ -6951,25 +7464,34 @@
         <v>0</v>
       </c>
       <c r="X64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="6" t="n">
         <v>252</v>
       </c>
-      <c r="Y64" s="5" t="inlineStr">
+      <c r="AB64" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z64" s="5" t="inlineStr">
+      <c r="AC64" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA64" s="5" t="inlineStr">
+      <c r="AD64" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB64" s="5" t="inlineStr"/>
-      <c r="AC64" s="5" t="inlineStr">
+      <c r="AE64" s="5" t="inlineStr"/>
+      <c r="AF64" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089971000197252</t>
         </is>
@@ -7060,25 +7582,34 @@
         <v>0</v>
       </c>
       <c r="X65" s="6" t="n">
+        <v>822.1900000000001</v>
+      </c>
+      <c r="Y65" s="6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Z65" s="6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA65" s="6" t="n">
         <v>1089</v>
       </c>
-      <c r="Y65" s="5" t="inlineStr">
+      <c r="AB65" s="5" t="inlineStr">
         <is>
           <t>201 - VENDA S/ ST - FORA DO ESTADO</t>
         </is>
       </c>
-      <c r="Z65" s="5" t="inlineStr">
+      <c r="AC65" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA65" s="5" t="inlineStr">
+      <c r="AD65" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB65" s="5" t="inlineStr"/>
-      <c r="AC65" s="5" t="inlineStr">
+      <c r="AE65" s="5" t="inlineStr"/>
+      <c r="AF65" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089981000186398</t>
         </is>
@@ -7169,29 +7700,38 @@
         <v>0</v>
       </c>
       <c r="X66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="6" t="n">
         <v>948</v>
       </c>
-      <c r="Y66" s="5" t="inlineStr">
+      <c r="AB66" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z66" s="5" t="inlineStr">
+      <c r="AC66" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA66" s="5" t="inlineStr">
+      <c r="AD66" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB66" s="5" t="inlineStr">
+      <c r="AE66" s="5" t="inlineStr">
         <is>
           <t>[ALTA] Industrialização x retorno: Item 1 (FRASCO IMPRESSO OX 20V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 6124 de industrialização - o mesmo item foi devolvido também na NF 9005 (6902). Retorno de insumo é 5902/6902; como está, R$ 948.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
         </is>
       </c>
-      <c r="AC66" s="5" t="inlineStr">
+      <c r="AF66" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000089991000116443</t>
         </is>
@@ -7282,29 +7822,38 @@
         <v>0</v>
       </c>
       <c r="X67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="6" t="n">
         <v>556.5</v>
       </c>
-      <c r="Y67" s="5" t="inlineStr">
+      <c r="AB67" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z67" s="5" t="inlineStr">
+      <c r="AC67" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA67" s="5" t="inlineStr">
+      <c r="AD67" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB67" s="5" t="inlineStr">
+      <c r="AE67" s="5" t="inlineStr">
         <is>
           <t>[ALTA] Industrialização x retorno: Item 1 (FRASCO IMPRESSO OX 20V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 9002 (5902). Retorno de insumo é 5902/6902; como está, R$ 556.50 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
         </is>
       </c>
-      <c r="AC67" s="5" t="inlineStr">
+      <c r="AF67" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090001000116462</t>
         </is>
@@ -7395,25 +7944,34 @@
         <v>0</v>
       </c>
       <c r="X68" s="6" t="n">
+        <v>3230.02</v>
+      </c>
+      <c r="Y68" s="6" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="Z68" s="6" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="AA68" s="6" t="n">
         <v>3691.45</v>
       </c>
-      <c r="Y68" s="5" t="inlineStr">
+      <c r="AB68" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z68" s="5" t="inlineStr">
+      <c r="AC68" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA68" s="5" t="inlineStr">
+      <c r="AD68" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB68" s="5" t="inlineStr"/>
-      <c r="AC68" s="5" t="inlineStr">
+      <c r="AE68" s="5" t="inlineStr"/>
+      <c r="AF68" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090011000116478</t>
         </is>
@@ -7504,25 +8062,34 @@
         <v>0</v>
       </c>
       <c r="X69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="6" t="n">
         <v>556.5</v>
       </c>
-      <c r="Y69" s="5" t="inlineStr">
+      <c r="AB69" s="5" t="inlineStr">
         <is>
           <t>277 - RETORNO DE MERC NA INDUSTR -</t>
         </is>
       </c>
-      <c r="Z69" s="5" t="inlineStr">
+      <c r="AC69" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA69" s="5" t="inlineStr">
+      <c r="AD69" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB69" s="5" t="inlineStr"/>
-      <c r="AC69" s="5" t="inlineStr">
+      <c r="AE69" s="5" t="inlineStr"/>
+      <c r="AF69" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090021000116483</t>
         </is>
@@ -7613,29 +8180,38 @@
         <v>0</v>
       </c>
       <c r="X70" s="6" t="n">
+        <v>89.44</v>
+      </c>
+      <c r="Y70" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z70" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AA70" s="6" t="n">
         <v>156.77</v>
       </c>
-      <c r="Y70" s="5" t="inlineStr">
+      <c r="AB70" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z70" s="5" t="inlineStr">
+      <c r="AC70" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA70" s="5" t="inlineStr">
+      <c r="AD70" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB70" s="5" t="inlineStr">
+      <c r="AE70" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 4 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC70" s="5" t="inlineStr">
+      <c r="AF70" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090031000162296</t>
         </is>
@@ -7726,25 +8302,34 @@
         <v>0</v>
       </c>
       <c r="X71" s="6" t="n">
+        <v>5062.16</v>
+      </c>
+      <c r="Y71" s="6" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="Z71" s="6" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="AA71" s="6" t="n">
         <v>6288.4</v>
       </c>
-      <c r="Y71" s="5" t="inlineStr">
+      <c r="AB71" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z71" s="5" t="inlineStr">
+      <c r="AC71" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA71" s="5" t="inlineStr">
+      <c r="AD71" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB71" s="5" t="inlineStr"/>
-      <c r="AC71" s="5" t="inlineStr">
+      <c r="AE71" s="5" t="inlineStr"/>
+      <c r="AF71" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090041000116496</t>
         </is>
@@ -7835,25 +8420,34 @@
         <v>0</v>
       </c>
       <c r="X72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="6" t="n">
         <v>948</v>
       </c>
-      <c r="Y72" s="5" t="inlineStr">
+      <c r="AB72" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z72" s="5" t="inlineStr">
+      <c r="AC72" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA72" s="5" t="inlineStr">
+      <c r="AD72" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB72" s="5" t="inlineStr"/>
-      <c r="AC72" s="5" t="inlineStr">
+      <c r="AE72" s="5" t="inlineStr"/>
+      <c r="AF72" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090051000116507</t>
         </is>
@@ -7944,29 +8538,38 @@
         <v>0</v>
       </c>
       <c r="X73" s="6" t="n">
+        <v>172.72</v>
+      </c>
+      <c r="Y73" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z73" s="6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA73" s="6" t="n">
         <v>302.73</v>
       </c>
-      <c r="Y73" s="5" t="inlineStr">
+      <c r="AB73" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z73" s="5" t="inlineStr">
+      <c r="AC73" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA73" s="5" t="inlineStr">
+      <c r="AD73" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB73" s="5" t="inlineStr">
+      <c r="AE73" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC73" s="5" t="inlineStr">
+      <c r="AF73" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090061000162328</t>
         </is>
@@ -8057,25 +8660,34 @@
         <v>0</v>
       </c>
       <c r="X74" s="6" t="n">
+        <v>1244.25</v>
+      </c>
+      <c r="Y74" s="6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z74" s="6" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="AA74" s="6" t="n">
         <v>1422</v>
       </c>
-      <c r="Y74" s="5" t="inlineStr">
+      <c r="AB74" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z74" s="5" t="inlineStr">
+      <c r="AC74" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA74" s="5" t="inlineStr">
+      <c r="AD74" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB74" s="5" t="inlineStr"/>
-      <c r="AC74" s="5" t="inlineStr">
+      <c r="AE74" s="5" t="inlineStr"/>
+      <c r="AF74" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090071000170263</t>
         </is>
@@ -8166,25 +8778,34 @@
         <v>0</v>
       </c>
       <c r="X75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="6" t="n">
         <v>149.4</v>
       </c>
-      <c r="Y75" s="5" t="inlineStr">
+      <c r="AB75" s="5" t="inlineStr">
         <is>
           <t>277 - RETORNO DE MERC NA INDUSTR -</t>
         </is>
       </c>
-      <c r="Z75" s="5" t="inlineStr">
+      <c r="AC75" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA75" s="5" t="inlineStr">
+      <c r="AD75" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB75" s="5" t="inlineStr"/>
-      <c r="AC75" s="5" t="inlineStr">
+      <c r="AE75" s="5" t="inlineStr"/>
+      <c r="AF75" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090081000170279</t>
         </is>
@@ -8275,29 +8896,38 @@
         <v>0</v>
       </c>
       <c r="X76" s="6" t="n">
+        <v>872.61</v>
+      </c>
+      <c r="Y76" s="6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Z76" s="6" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AA76" s="6" t="n">
         <v>1529.47</v>
       </c>
-      <c r="Y76" s="5" t="inlineStr">
+      <c r="AB76" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z76" s="5" t="inlineStr">
+      <c r="AC76" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA76" s="5" t="inlineStr">
+      <c r="AD76" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB76" s="5" t="inlineStr">
+      <c r="AE76" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 5 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC76" s="5" t="inlineStr">
+      <c r="AF76" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090091000162354</t>
         </is>
@@ -8388,25 +9018,34 @@
         <v>0</v>
       </c>
       <c r="X77" s="6" t="n">
+        <v>8751.610000000001</v>
+      </c>
+      <c r="Y77" s="6" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="Z77" s="6" t="n">
+        <v>78.73999999999999</v>
+      </c>
+      <c r="AA77" s="6" t="n">
         <v>10871.57</v>
       </c>
-      <c r="Y77" s="5" t="inlineStr">
+      <c r="AB77" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z77" s="5" t="inlineStr">
+      <c r="AC77" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA77" s="5" t="inlineStr">
+      <c r="AD77" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB77" s="5" t="inlineStr"/>
-      <c r="AC77" s="5" t="inlineStr">
+      <c r="AE77" s="5" t="inlineStr"/>
+      <c r="AF77" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090101000217818</t>
         </is>
@@ -8497,25 +9136,34 @@
         <v>0</v>
       </c>
       <c r="X78" s="6" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="Y78" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z78" s="6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA78" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="Y78" s="5" t="inlineStr">
+      <c r="AB78" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z78" s="5" t="inlineStr">
+      <c r="AC78" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA78" s="5" t="inlineStr">
+      <c r="AD78" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB78" s="5" t="inlineStr"/>
-      <c r="AC78" s="5" t="inlineStr">
+      <c r="AE78" s="5" t="inlineStr"/>
+      <c r="AF78" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090111000162379</t>
         </is>
@@ -8606,25 +9254,34 @@
         <v>0</v>
       </c>
       <c r="X79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="6" t="n">
         <v>982.8</v>
       </c>
-      <c r="Y79" s="5" t="inlineStr">
+      <c r="AB79" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z79" s="5" t="inlineStr">
+      <c r="AC79" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA79" s="5" t="inlineStr">
+      <c r="AD79" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB79" s="5" t="inlineStr"/>
-      <c r="AC79" s="5" t="inlineStr">
+      <c r="AE79" s="5" t="inlineStr"/>
+      <c r="AF79" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090121000217839</t>
         </is>
@@ -8715,29 +9372,38 @@
         <v>0</v>
       </c>
       <c r="X80" s="6" t="n">
+        <v>352.85</v>
+      </c>
+      <c r="Y80" s="6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z80" s="6" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA80" s="6" t="n">
         <v>618.45</v>
       </c>
-      <c r="Y80" s="5" t="inlineStr">
+      <c r="AB80" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z80" s="5" t="inlineStr">
+      <c r="AC80" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA80" s="5" t="inlineStr">
+      <c r="AD80" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB80" s="5" t="inlineStr">
+      <c r="AE80" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC80" s="5" t="inlineStr">
+      <c r="AF80" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090131000162390</t>
         </is>
@@ -8828,29 +9494,38 @@
         <v>0</v>
       </c>
       <c r="X81" s="6" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="Y81" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z81" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AA81" s="6" t="n">
         <v>148.13</v>
       </c>
-      <c r="Y81" s="5" t="inlineStr">
+      <c r="AB81" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z81" s="5" t="inlineStr">
+      <c r="AC81" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA81" s="5" t="inlineStr">
+      <c r="AD81" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB81" s="5" t="inlineStr">
+      <c r="AE81" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC81" s="5" t="inlineStr">
+      <c r="AF81" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090141000162400</t>
         </is>
@@ -8941,25 +9616,34 @@
         <v>0</v>
       </c>
       <c r="X82" s="6" t="n">
+        <v>643.26</v>
+      </c>
+      <c r="Y82" s="6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Z82" s="6" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="AA82" s="6" t="n">
         <v>852</v>
       </c>
-      <c r="Y82" s="5" t="inlineStr">
+      <c r="AB82" s="5" t="inlineStr">
         <is>
           <t>201 - VENDA S/ ST - FORA DO ESTADO</t>
         </is>
       </c>
-      <c r="Z82" s="5" t="inlineStr">
+      <c r="AC82" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA82" s="5" t="inlineStr">
+      <c r="AD82" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB82" s="5" t="inlineStr"/>
-      <c r="AC82" s="5" t="inlineStr">
+      <c r="AE82" s="5" t="inlineStr"/>
+      <c r="AF82" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090151000189365</t>
         </is>
@@ -9050,25 +9734,34 @@
         <v>0</v>
       </c>
       <c r="X83" s="6" t="n">
+        <v>5078.88</v>
+      </c>
+      <c r="Y83" s="6" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="Z83" s="6" t="n">
+        <v>45.72</v>
+      </c>
+      <c r="AA83" s="6" t="n">
         <v>6727</v>
       </c>
-      <c r="Y83" s="5" t="inlineStr">
+      <c r="AB83" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z83" s="5" t="inlineStr">
+      <c r="AC83" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA83" s="5" t="inlineStr">
+      <c r="AD83" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB83" s="5" t="inlineStr"/>
-      <c r="AC83" s="5" t="inlineStr">
+      <c r="AE83" s="5" t="inlineStr"/>
+      <c r="AF83" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090161000163304</t>
         </is>
@@ -9159,29 +9852,38 @@
         <v>0</v>
       </c>
       <c r="X84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="6" t="n">
         <v>547.2</v>
       </c>
-      <c r="Y84" s="5" t="inlineStr">
+      <c r="AB84" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z84" s="5" t="inlineStr">
+      <c r="AC84" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA84" s="5" t="inlineStr">
+      <c r="AD84" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB84" s="5" t="inlineStr">
+      <c r="AE84" s="5" t="inlineStr">
         <is>
           <t>[BAIXA] Industrialização x retorno: Informações complementares citam a industrialização na NF 9015, que é de FABIANO RODRIGUES AMARAL (CFOP 6101); a do cliente é a NF 9016 - informativo, escriturado como está no XML</t>
         </is>
       </c>
-      <c r="AC84" s="5" t="inlineStr">
+      <c r="AF84" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090171000163310</t>
         </is>
@@ -9272,29 +9974,38 @@
         <v>0</v>
       </c>
       <c r="X85" s="6" t="n">
+        <v>79.59</v>
+      </c>
+      <c r="Y85" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z85" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AA85" s="6" t="n">
         <v>139.49</v>
       </c>
-      <c r="Y85" s="5" t="inlineStr">
+      <c r="AB85" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z85" s="5" t="inlineStr">
+      <c r="AC85" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA85" s="5" t="inlineStr">
+      <c r="AD85" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB85" s="5" t="inlineStr">
+      <c r="AE85" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC85" s="5" t="inlineStr">
+      <c r="AF85" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090181000162442</t>
         </is>
@@ -9385,29 +10096,38 @@
         <v>0</v>
       </c>
       <c r="X86" s="6" t="n">
+        <v>3434.83</v>
+      </c>
+      <c r="Y86" s="6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Z86" s="6" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="AA86" s="6" t="n">
         <v>6020.39</v>
       </c>
-      <c r="Y86" s="5" t="inlineStr">
+      <c r="AB86" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z86" s="5" t="inlineStr">
+      <c r="AC86" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA86" s="5" t="inlineStr">
+      <c r="AD86" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB86" s="5" t="inlineStr">
+      <c r="AE86" s="5" t="inlineStr">
         <is>
           <t>[MÉDIA] CFOP revenda x produção: 41 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="AC86" s="5" t="inlineStr">
+      <c r="AF86" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090191000162458</t>
         </is>
@@ -9498,29 +10218,38 @@
         <v>0</v>
       </c>
       <c r="X87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="Y87" s="5" t="inlineStr">
+      <c r="AB87" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z87" s="5" t="inlineStr">
+      <c r="AC87" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA87" s="5" t="inlineStr">
+      <c r="AD87" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB87" s="5" t="inlineStr">
+      <c r="AE87" s="5" t="inlineStr">
         <is>
           <t>[ALTA] Industrialização x retorno: Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 6124 de industrialização - o mesmo item foi devolvido também na NF 9026 (6902). Retorno de insumo é 5902/6902; como está, R$ 600.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
         </is>
       </c>
-      <c r="AC87" s="5" t="inlineStr">
+      <c r="AF87" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090201000116651</t>
         </is>
@@ -9611,29 +10340,38 @@
         <v>0</v>
       </c>
       <c r="X88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="Y88" s="5" t="inlineStr">
+      <c r="AB88" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z88" s="5" t="inlineStr">
+      <c r="AC88" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA88" s="5" t="inlineStr">
+      <c r="AD88" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB88" s="5" t="inlineStr">
+      <c r="AE88" s="5" t="inlineStr">
         <is>
           <t>[ALTA] Industrialização x retorno: Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 9024 (5902). Retorno de insumo é 5902/6902; como está, R$ 300.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
         </is>
       </c>
-      <c r="AC88" s="5" t="inlineStr">
+      <c r="AF88" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090211000116675</t>
         </is>
@@ -9724,25 +10462,34 @@
         <v>0</v>
       </c>
       <c r="X89" s="6" t="n">
+        <v>2235.84</v>
+      </c>
+      <c r="Y89" s="6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Z89" s="6" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="AA89" s="6" t="n">
         <v>3288</v>
       </c>
-      <c r="Y89" s="5" t="inlineStr">
+      <c r="AB89" s="5" t="inlineStr">
         <is>
           <t>200 - VENDAS S/ ST - DENTRO DO EST</t>
         </is>
       </c>
-      <c r="Z89" s="5" t="inlineStr">
+      <c r="AC89" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA89" s="5" t="inlineStr">
+      <c r="AD89" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB89" s="5" t="inlineStr"/>
-      <c r="AC89" s="5" t="inlineStr">
+      <c r="AE89" s="5" t="inlineStr"/>
+      <c r="AF89" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090221000192042</t>
         </is>
@@ -9833,25 +10580,34 @@
         <v>0</v>
       </c>
       <c r="X90" s="6" t="n">
+        <v>1662.5</v>
+      </c>
+      <c r="Y90" s="6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z90" s="6" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AA90" s="6" t="n">
         <v>1900</v>
       </c>
-      <c r="Y90" s="5" t="inlineStr">
+      <c r="AB90" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z90" s="5" t="inlineStr">
+      <c r="AC90" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA90" s="5" t="inlineStr">
+      <c r="AD90" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB90" s="5" t="inlineStr"/>
-      <c r="AC90" s="5" t="inlineStr">
+      <c r="AE90" s="5" t="inlineStr"/>
+      <c r="AF90" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090231000116696</t>
         </is>
@@ -9942,25 +10698,34 @@
         <v>0</v>
       </c>
       <c r="X91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="Y91" s="5" t="inlineStr">
+      <c r="AB91" s="5" t="inlineStr">
         <is>
           <t>277 - RETORNO DE MERC NA INDUSTR -</t>
         </is>
       </c>
-      <c r="Z91" s="5" t="inlineStr">
+      <c r="AC91" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA91" s="5" t="inlineStr">
+      <c r="AD91" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB91" s="5" t="inlineStr"/>
-      <c r="AC91" s="5" t="inlineStr">
+      <c r="AE91" s="5" t="inlineStr"/>
+      <c r="AF91" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090241000116707</t>
         </is>
@@ -10051,25 +10816,34 @@
         <v>0</v>
       </c>
       <c r="X92" s="6" t="n">
+        <v>3203.9</v>
+      </c>
+      <c r="Y92" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z92" s="6" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="AA92" s="6" t="n">
         <v>3980</v>
       </c>
-      <c r="Y92" s="5" t="inlineStr">
+      <c r="AB92" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z92" s="5" t="inlineStr">
+      <c r="AC92" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA92" s="5" t="inlineStr">
+      <c r="AD92" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB92" s="5" t="inlineStr"/>
-      <c r="AC92" s="5" t="inlineStr">
+      <c r="AE92" s="5" t="inlineStr"/>
+      <c r="AF92" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090251000116704</t>
         </is>
@@ -10160,25 +10934,34 @@
         <v>0</v>
       </c>
       <c r="X93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="Y93" s="5" t="inlineStr">
+      <c r="AB93" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z93" s="5" t="inlineStr">
+      <c r="AC93" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA93" s="5" t="inlineStr">
+      <c r="AD93" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB93" s="5" t="inlineStr"/>
-      <c r="AC93" s="5" t="inlineStr">
+      <c r="AE93" s="5" t="inlineStr"/>
+      <c r="AF93" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090261000116710</t>
         </is>
@@ -10269,25 +11052,34 @@
         <v>0</v>
       </c>
       <c r="X94" s="6" t="n">
+        <v>1830.12</v>
+      </c>
+      <c r="Y94" s="6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z94" s="6" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="AA94" s="6" t="n">
         <v>2424</v>
       </c>
-      <c r="Y94" s="5" t="inlineStr">
+      <c r="AB94" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z94" s="5" t="inlineStr">
+      <c r="AC94" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA94" s="5" t="inlineStr">
+      <c r="AD94" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB94" s="5" t="inlineStr"/>
-      <c r="AC94" s="5" t="inlineStr">
+      <c r="AE94" s="5" t="inlineStr"/>
+      <c r="AF94" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090271000116792</t>
         </is>
@@ -10378,25 +11170,34 @@
         <v>0</v>
       </c>
       <c r="X95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="6" t="n">
         <v>500.1</v>
       </c>
-      <c r="Y95" s="5" t="inlineStr">
+      <c r="AB95" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z95" s="5" t="inlineStr">
+      <c r="AC95" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA95" s="5" t="inlineStr">
+      <c r="AD95" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB95" s="5" t="inlineStr"/>
-      <c r="AC95" s="5" t="inlineStr">
+      <c r="AE95" s="5" t="inlineStr"/>
+      <c r="AF95" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090281000116803</t>
         </is>
@@ -10487,25 +11288,34 @@
         <v>0</v>
       </c>
       <c r="X96" s="6" t="n">
+        <v>1171.21</v>
+      </c>
+      <c r="Y96" s="6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z96" s="6" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="AA96" s="6" t="n">
         <v>1551.26</v>
       </c>
-      <c r="Y96" s="5" t="inlineStr">
+      <c r="AB96" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z96" s="5" t="inlineStr">
+      <c r="AC96" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA96" s="5" t="inlineStr">
+      <c r="AD96" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB96" s="5" t="inlineStr"/>
-      <c r="AC96" s="5" t="inlineStr">
+      <c r="AE96" s="5" t="inlineStr"/>
+      <c r="AF96" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090291000186701</t>
         </is>
@@ -10596,25 +11406,34 @@
         <v>0</v>
       </c>
       <c r="X97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="6" t="n">
         <v>133.2</v>
       </c>
-      <c r="Y97" s="5" t="inlineStr">
+      <c r="AB97" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z97" s="5" t="inlineStr">
+      <c r="AC97" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA97" s="5" t="inlineStr">
+      <c r="AD97" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB97" s="5" t="inlineStr"/>
-      <c r="AC97" s="5" t="inlineStr">
+      <c r="AE97" s="5" t="inlineStr"/>
+      <c r="AF97" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090301000186710</t>
         </is>
@@ -10705,25 +11524,34 @@
         <v>0</v>
       </c>
       <c r="X98" s="6" t="n">
+        <v>2097.91</v>
+      </c>
+      <c r="Y98" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z98" s="6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AA98" s="6" t="n">
         <v>1198.8</v>
       </c>
-      <c r="Y98" s="5" t="inlineStr">
+      <c r="AB98" s="5" t="inlineStr">
         <is>
           <t>254 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z98" s="5" t="inlineStr">
+      <c r="AC98" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA98" s="5" t="inlineStr">
+      <c r="AD98" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB98" s="5" t="inlineStr"/>
-      <c r="AC98" s="5" t="inlineStr">
+      <c r="AE98" s="5" t="inlineStr"/>
+      <c r="AF98" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090311000119484</t>
         </is>
@@ -10814,25 +11642,34 @@
         <v>0</v>
       </c>
       <c r="X99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="6" t="n">
         <v>348</v>
       </c>
-      <c r="Y99" s="5" t="inlineStr">
+      <c r="AB99" s="5" t="inlineStr">
         <is>
           <t>277 - RETORNO DE MERC NA INDUSTR -</t>
         </is>
       </c>
-      <c r="Z99" s="5" t="inlineStr">
+      <c r="AC99" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA99" s="5" t="inlineStr">
+      <c r="AD99" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB99" s="5" t="inlineStr"/>
-      <c r="AC99" s="5" t="inlineStr">
+      <c r="AE99" s="5" t="inlineStr"/>
+      <c r="AF99" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090321000119490</t>
         </is>
@@ -10923,25 +11760,34 @@
         <v>0</v>
       </c>
       <c r="X100" s="6" t="n">
+        <v>1907.85</v>
+      </c>
+      <c r="Y100" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z100" s="6" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="AA100" s="6" t="n">
         <v>2370</v>
       </c>
-      <c r="Y100" s="5" t="inlineStr">
+      <c r="AB100" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z100" s="5" t="inlineStr">
+      <c r="AC100" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA100" s="5" t="inlineStr">
+      <c r="AD100" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB100" s="5" t="inlineStr"/>
-      <c r="AC100" s="5" t="inlineStr">
+      <c r="AE100" s="5" t="inlineStr"/>
+      <c r="AF100" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090331000116781</t>
         </is>
@@ -11032,25 +11878,34 @@
         <v>0</v>
       </c>
       <c r="X101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="6" t="n">
         <v>427.2</v>
       </c>
-      <c r="Y101" s="5" t="inlineStr">
+      <c r="AB101" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z101" s="5" t="inlineStr">
+      <c r="AC101" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA101" s="5" t="inlineStr">
+      <c r="AD101" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB101" s="5" t="inlineStr"/>
-      <c r="AC101" s="5" t="inlineStr">
+      <c r="AE101" s="5" t="inlineStr"/>
+      <c r="AF101" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090341000116797</t>
         </is>
@@ -11141,25 +11996,34 @@
         <v>0</v>
       </c>
       <c r="X102" s="6" t="n">
+        <v>3153.9</v>
+      </c>
+      <c r="Y102" s="6" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Z102" s="6" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="AA102" s="6" t="n">
         <v>3917.94</v>
       </c>
-      <c r="Y102" s="5" t="inlineStr">
+      <c r="AB102" s="5" t="inlineStr">
         <is>
           <t>255 - IND. EFETUADA PARA OUTRA EMP</t>
         </is>
       </c>
-      <c r="Z102" s="5" t="inlineStr">
+      <c r="AC102" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA102" s="5" t="inlineStr">
+      <c r="AD102" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB102" s="5" t="inlineStr"/>
-      <c r="AC102" s="5" t="inlineStr">
+      <c r="AE102" s="5" t="inlineStr"/>
+      <c r="AF102" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090351000187314</t>
         </is>
@@ -11250,25 +12114,34 @@
         <v>0</v>
       </c>
       <c r="X103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="6" t="n">
         <v>297.6</v>
       </c>
-      <c r="Y103" s="5" t="inlineStr">
+      <c r="AB103" s="5" t="inlineStr">
         <is>
           <t>217 - RETORNO REMESSA IND. ENCOMEN</t>
         </is>
       </c>
-      <c r="Z103" s="5" t="inlineStr">
+      <c r="AC103" s="5" t="inlineStr">
         <is>
           <t>Sim - como está no XML</t>
         </is>
       </c>
-      <c r="AA103" s="5" t="inlineStr">
+      <c r="AD103" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AB103" s="5" t="inlineStr"/>
-      <c r="AC103" s="5" t="inlineStr">
+      <c r="AE103" s="5" t="inlineStr"/>
+      <c r="AF103" s="5" t="inlineStr">
         <is>
           <t>41260933039048000162550010000090361000187320</t>
         </is>
@@ -11348,11 +12221,23 @@
         <f>SUMIF($E$5:$E$103,"Autorizada",X5:X103)</f>
         <v/>
       </c>
-      <c r="Y104" s="8" t="n"/>
-      <c r="Z104" s="8" t="n"/>
-      <c r="AA104" s="8" t="n"/>
+      <c r="Y104" s="9">
+        <f>SUMIF($E$5:$E$103,"Autorizada",Y5:Y103)</f>
+        <v/>
+      </c>
+      <c r="Z104" s="9">
+        <f>SUMIF($E$5:$E$103,"Autorizada",Z5:Z103)</f>
+        <v/>
+      </c>
+      <c r="AA104" s="9">
+        <f>SUMIF($E$5:$E$103,"Autorizada",AA5:AA103)</f>
+        <v/>
+      </c>
       <c r="AB104" s="8" t="n"/>
       <c r="AC104" s="8" t="n"/>
+      <c r="AD104" s="8" t="n"/>
+      <c r="AE104" s="8" t="n"/>
+      <c r="AF104" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -11399,8 +12284,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AC103"/>
-  <conditionalFormatting sqref="A5:AC103">
+  <autoFilter ref="A4:AF103"/>
+  <conditionalFormatting sqref="A5:AF103">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E5="Cancelada"</formula>
     </cfRule>

--- a/Cosmetici/Fiscal/2026-09/Relacao_Saidas_Cosmetici_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Relacao_Saidas_Cosmetici_09-2026.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>Importar no Domínio</t>
+          <t>Importar no Domínio (TXT)</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
